--- a/output/yearly_benthic_cover_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_56_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.40394281084178</v>
+        <v>45.43877048612569</v>
       </c>
       <c r="M2" t="n">
-        <v>99.10503865889169</v>
+        <v>99.24720843859791</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95209189948227</v>
+        <v>87.99398307402248</v>
       </c>
       <c r="C3" t="n">
-        <v>45.82536353593918</v>
+        <v>45.90449642333998</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228615936284659</v>
+        <v>2.228663447861512</v>
       </c>
       <c r="E3" t="n">
-        <v>5.643492394111038</v>
+        <v>5.690742453178022</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428719787615531</v>
+        <v>0.7428878159538376</v>
       </c>
       <c r="G3" t="n">
-        <v>33.93799280010607</v>
+        <v>33.96507014600136</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17211102303143</v>
+        <v>34.17283953387653</v>
       </c>
       <c r="I3" t="n">
-        <v>6.584057899927815</v>
+        <v>6.550730827439739</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642949867259706</v>
+        <v>4.643048849711485</v>
       </c>
       <c r="K3" t="n">
-        <v>12.04790810051772</v>
+        <v>12.00601692597751</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89038228729977</v>
+        <v>48.85434192001533</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636539237567</v>
+        <v>106.7648552693328</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07969191760318</v>
+        <v>87.05287406336087</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5950256134853</v>
+        <v>42.59607857836641</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186706812740134</v>
+        <v>2.183150644076909</v>
       </c>
       <c r="E4" t="n">
-        <v>6.453743639067987</v>
+        <v>6.486258059557808</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444354911503394</v>
+        <v>0.7444439110057739</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29978883236275</v>
+        <v>33.27145013147268</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2440325929156</v>
+        <v>34.2444199062656</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498262729676746</v>
+        <v>5.470376967196034</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652721819689621</v>
+        <v>4.652774443786086</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92030808239682</v>
+        <v>12.94712593663913</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30177580689766</v>
+        <v>44.2748307397878</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81710950277977</v>
+        <v>99.81803525479333</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.98638985023693</v>
+        <v>85.88954861076616</v>
       </c>
       <c r="C5" t="n">
-        <v>42.35502030929893</v>
+        <v>42.28175187229567</v>
       </c>
       <c r="D5" t="n">
-        <v>2.133493058341517</v>
+        <v>2.126357908559771</v>
       </c>
       <c r="E5" t="n">
-        <v>7.061697477284953</v>
+        <v>7.078644932349406</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457601145556256</v>
+        <v>0.7457633078643321</v>
       </c>
       <c r="G5" t="n">
-        <v>32.48943475374227</v>
+        <v>32.40592274667448</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30496526955877</v>
+        <v>34.30511216175928</v>
       </c>
       <c r="I5" t="n">
-        <v>4.59003846078113</v>
+        <v>4.566726879406819</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66100071597266</v>
+        <v>4.661020674152074</v>
       </c>
       <c r="K5" t="n">
-        <v>14.0136101497631</v>
+        <v>14.11045138923385</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47864002066918</v>
+        <v>43.45584182271504</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84727047973119</v>
+        <v>99.84804508424456</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.69959069218895</v>
+        <v>84.52616348409049</v>
       </c>
       <c r="C6" t="n">
-        <v>41.78109158765155</v>
+        <v>41.62757139091218</v>
       </c>
       <c r="D6" t="n">
-        <v>2.07074956218364</v>
+        <v>2.059778865416283</v>
       </c>
       <c r="E6" t="n">
-        <v>7.492487790330394</v>
+        <v>7.492224251405236</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468844241448215</v>
+        <v>0.7468842021469612</v>
       </c>
       <c r="G6" t="n">
-        <v>31.53395907657852</v>
+        <v>31.39125098329447</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35668351066178</v>
+        <v>34.35667329876021</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830798677384648</v>
+        <v>3.811325619648808</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668027650905135</v>
+        <v>4.668026263418506</v>
       </c>
       <c r="K6" t="n">
-        <v>15.30040930781107</v>
+        <v>15.4738365159095</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79099803618237</v>
+        <v>42.77173856875037</v>
       </c>
       <c r="M6" t="n">
-        <v>99.872498931645</v>
+        <v>99.87314647557206</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.22525187100273</v>
+        <v>82.99393572618233</v>
       </c>
       <c r="C7" t="n">
-        <v>40.90179740391013</v>
+        <v>40.68726132486154</v>
       </c>
       <c r="D7" t="n">
-        <v>1.999018513079826</v>
+        <v>1.985227770872092</v>
       </c>
       <c r="E7" t="n">
-        <v>7.765683508803246</v>
+        <v>7.751079559832526</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478406065607828</v>
+        <v>0.7478381723781051</v>
       </c>
       <c r="G7" t="n">
-        <v>30.44161840522547</v>
+        <v>30.2550843009341</v>
       </c>
       <c r="H7" t="n">
-        <v>34.400667901796</v>
+        <v>34.40055592939284</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196419144532514</v>
+        <v>3.180161415409504</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674003791004893</v>
+        <v>4.673988577363155</v>
       </c>
       <c r="K7" t="n">
-        <v>16.7747481289973</v>
+        <v>17.00606427381769</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21704339272078</v>
+        <v>42.20080424521939</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89358892562819</v>
+        <v>99.89412984389861</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.09518649457571</v>
+        <v>88.02653912251581</v>
       </c>
       <c r="C8" t="n">
-        <v>43.2012374366271</v>
+        <v>43.06110817642814</v>
       </c>
       <c r="D8" t="n">
-        <v>2.003287240357296</v>
+        <v>1.989522682423386</v>
       </c>
       <c r="E8" t="n">
-        <v>9.597048798573798</v>
+        <v>9.636515770584772</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494375540505321</v>
+        <v>0.7494560717708959</v>
       </c>
       <c r="G8" t="n">
-        <v>30.94371626625162</v>
+        <v>30.77877356691524</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47412748632447</v>
+        <v>34.47497930146122</v>
       </c>
       <c r="I8" t="n">
-        <v>5.643584436202174</v>
+        <v>5.713191280792201</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683984712815827</v>
+        <v>4.684100448568098</v>
       </c>
       <c r="K8" t="n">
-        <v>11.90481350542427</v>
+        <v>11.97346087748419</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70623043326648</v>
+        <v>44.77540235127054</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81228137531785</v>
+        <v>99.80997140518286</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.18975363793253</v>
+        <v>86.152959601463</v>
       </c>
       <c r="C9" t="n">
-        <v>42.17188817428479</v>
+        <v>42.07418735964036</v>
       </c>
       <c r="D9" t="n">
-        <v>1.917052262024504</v>
+        <v>1.905128619673719</v>
       </c>
       <c r="E9" t="n">
-        <v>9.969186606860642</v>
+        <v>10.02270515246287</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508031523723659</v>
+        <v>0.7508391698670696</v>
       </c>
       <c r="G9" t="n">
-        <v>29.61169026019552</v>
+        <v>29.47316103446599</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53694500912883</v>
+        <v>34.53860181388521</v>
       </c>
       <c r="I9" t="n">
-        <v>4.711556645023369</v>
+        <v>4.76977899943895</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692519702327288</v>
+        <v>4.692744811669184</v>
       </c>
       <c r="K9" t="n">
-        <v>13.81024636206747</v>
+        <v>13.84704039853704</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86109922930878</v>
+        <v>43.92007248402282</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84323376566104</v>
+        <v>99.84130024220021</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.09527714037756</v>
+        <v>84.14603410711103</v>
       </c>
       <c r="C10" t="n">
-        <v>40.80863865126243</v>
+        <v>40.80737778759535</v>
       </c>
       <c r="D10" t="n">
-        <v>1.82313244414685</v>
+        <v>1.815635791677242</v>
       </c>
       <c r="E10" t="n">
-        <v>10.13618119453007</v>
+        <v>10.21540573126122</v>
       </c>
       <c r="F10" t="n">
-        <v>0.75197344053344</v>
+        <v>0.7520232835276309</v>
       </c>
       <c r="G10" t="n">
-        <v>28.16096061062925</v>
+        <v>28.08866840560523</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59077826453823</v>
+        <v>34.59307104227103</v>
       </c>
       <c r="I10" t="n">
-        <v>3.932417182665717</v>
+        <v>3.981084330720992</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699834003334001</v>
+        <v>4.700145522047692</v>
       </c>
       <c r="K10" t="n">
-        <v>15.90472285962244</v>
+        <v>15.85396589288896</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15576191564226</v>
+        <v>43.20616245842019</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86912342652712</v>
+        <v>99.8675061389045</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.9221626134922</v>
+        <v>81.96444189033451</v>
       </c>
       <c r="C11" t="n">
-        <v>39.24530221610229</v>
+        <v>39.24306937456159</v>
       </c>
       <c r="D11" t="n">
-        <v>1.726684817340183</v>
+        <v>1.719226404332264</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14685369152843</v>
+        <v>10.22664799286931</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529774496259349</v>
+        <v>0.7530392772377923</v>
       </c>
       <c r="G11" t="n">
-        <v>26.67118523626679</v>
+        <v>26.59717362194102</v>
       </c>
       <c r="H11" t="n">
-        <v>34.636962682793</v>
+        <v>34.63980675293846</v>
       </c>
       <c r="I11" t="n">
-        <v>3.28138967577579</v>
+        <v>3.322052358279461</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706109060162095</v>
+        <v>4.706495482736201</v>
       </c>
       <c r="K11" t="n">
-        <v>18.07783738650777</v>
+        <v>18.0355581096655</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56762658676033</v>
+        <v>42.61078683991956</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8907661893704</v>
+        <v>99.88941432414664</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.51817267159834</v>
+        <v>79.64080884106338</v>
       </c>
       <c r="C12" t="n">
-        <v>37.34945981894742</v>
+        <v>37.43385040798141</v>
       </c>
       <c r="D12" t="n">
-        <v>1.620851419629401</v>
+        <v>1.617454055758413</v>
       </c>
       <c r="E12" t="n">
-        <v>9.981195899492919</v>
+        <v>10.08319665443605</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538415595476613</v>
+        <v>0.7539128306100839</v>
       </c>
       <c r="G12" t="n">
-        <v>25.0364328331757</v>
+        <v>25.0227115161297</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67671173919241</v>
+        <v>34.67999020806388</v>
       </c>
       <c r="I12" t="n">
-        <v>2.73762947338737</v>
+        <v>2.771588384752227</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711509747172884</v>
+        <v>4.711955191313023</v>
       </c>
       <c r="K12" t="n">
-        <v>20.48182732840166</v>
+        <v>20.35919115893662</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07756313943491</v>
+        <v>42.11467920090755</v>
       </c>
       <c r="M12" t="n">
-        <v>99.908850286784</v>
+        <v>99.90772076782558</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.12479445122798</v>
+        <v>77.15164819400046</v>
       </c>
       <c r="C13" t="n">
-        <v>35.37916980722357</v>
+        <v>35.37305724108694</v>
       </c>
       <c r="D13" t="n">
-        <v>1.516465889347891</v>
+        <v>1.509326903269579</v>
       </c>
       <c r="E13" t="n">
-        <v>9.71899185399476</v>
+        <v>9.794460127348422</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545855830441234</v>
+        <v>0.7546659013103798</v>
       </c>
       <c r="G13" t="n">
-        <v>23.42404487089967</v>
+        <v>23.34993785424042</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71093682002966</v>
+        <v>34.71463146027749</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283609539886099</v>
+        <v>2.311964064364299</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716159894025772</v>
+        <v>4.716661883189873</v>
       </c>
       <c r="K13" t="n">
-        <v>22.87520554877202</v>
+        <v>22.84835180599953</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66957938085476</v>
+        <v>41.70160238667042</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92395473685035</v>
+        <v>99.9230114337569</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.73032978306621</v>
+        <v>83.66664380949176</v>
       </c>
       <c r="C14" t="n">
-        <v>39.43649525497322</v>
+        <v>39.44064934358026</v>
       </c>
       <c r="D14" t="n">
-        <v>1.518282711279999</v>
+        <v>1.511087719767215</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99503445893733</v>
+        <v>12.06838663780955</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554896242405377</v>
+        <v>0.7555463124170473</v>
       </c>
       <c r="G14" t="n">
-        <v>25.21493587307373</v>
+        <v>25.15164106884106</v>
       </c>
       <c r="H14" t="n">
-        <v>36.51535023176304</v>
+        <v>36.52959299549027</v>
       </c>
       <c r="I14" t="n">
-        <v>3.009426732268225</v>
+        <v>2.928224622560059</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721810151503361</v>
+        <v>4.722164452606544</v>
       </c>
       <c r="K14" t="n">
-        <v>16.26967021693378</v>
+        <v>16.33335619050827</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19364034264759</v>
+        <v>44.12850071700835</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89980581455458</v>
+        <v>99.90250625109688</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.95525960551745</v>
+        <v>82.76705857061333</v>
       </c>
       <c r="C15" t="n">
-        <v>39.12664842502008</v>
+        <v>38.97638106737402</v>
       </c>
       <c r="D15" t="n">
-        <v>1.489398142265756</v>
+        <v>1.47540472746471</v>
       </c>
       <c r="E15" t="n">
-        <v>12.18523248941213</v>
+        <v>12.20791077079678</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562517097719883</v>
+        <v>0.7562895582285908</v>
       </c>
       <c r="G15" t="n">
-        <v>24.73523433263959</v>
+        <v>24.57511784579381</v>
       </c>
       <c r="H15" t="n">
-        <v>36.55218438433721</v>
+        <v>36.58293828366421</v>
       </c>
       <c r="I15" t="n">
-        <v>2.51038536101585</v>
+        <v>2.442587645736555</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726573186074927</v>
+        <v>4.726809738928692</v>
       </c>
       <c r="K15" t="n">
-        <v>17.04474039448255</v>
+        <v>17.23294142938666</v>
       </c>
       <c r="L15" t="n">
-        <v>43.74501599348992</v>
+        <v>43.70933793039043</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91640481299254</v>
+        <v>99.91866042715111</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.52335273237361</v>
+        <v>80.17523481392472</v>
       </c>
       <c r="C16" t="n">
-        <v>37.08287443442003</v>
+        <v>36.76214742972534</v>
       </c>
       <c r="D16" t="n">
-        <v>1.396306627568636</v>
+        <v>1.376618182061155</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7725885008803</v>
+        <v>11.73005892663335</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569071886077173</v>
+        <v>0.7569301232262658</v>
       </c>
       <c r="G16" t="n">
-        <v>23.18921358434543</v>
+        <v>22.92967714082678</v>
       </c>
       <c r="H16" t="n">
-        <v>36.58386587735601</v>
+        <v>36.61392343944437</v>
       </c>
       <c r="I16" t="n">
-        <v>2.093801024817263</v>
+        <v>2.037213731568646</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730669928798234</v>
+        <v>4.730813270164161</v>
       </c>
       <c r="K16" t="n">
-        <v>19.47664726762641</v>
+        <v>19.82476518607529</v>
       </c>
       <c r="L16" t="n">
-        <v>43.37074537125868</v>
+        <v>43.34523772737336</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93026707330512</v>
+        <v>99.93215034317397</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.11332259183244</v>
+        <v>81.85285510841871</v>
       </c>
       <c r="C17" t="n">
-        <v>38.23817539184647</v>
+        <v>37.98630866452952</v>
       </c>
       <c r="D17" t="n">
-        <v>1.39750037683588</v>
+        <v>1.377755262668465</v>
       </c>
       <c r="E17" t="n">
-        <v>12.52021670842757</v>
+        <v>12.505778018668</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575542938952903</v>
+        <v>0.7575553442028772</v>
       </c>
       <c r="G17" t="n">
-        <v>23.59559510857852</v>
+        <v>23.37659656407796</v>
       </c>
       <c r="H17" t="n">
-        <v>37.00169893812419</v>
+        <v>37.07214599038526</v>
       </c>
       <c r="I17" t="n">
-        <v>2.106042829125423</v>
+        <v>2.028303027148171</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734714336845565</v>
+        <v>4.734720901267981</v>
       </c>
       <c r="K17" t="n">
-        <v>17.88667740816758</v>
+        <v>18.14714489158129</v>
       </c>
       <c r="L17" t="n">
-        <v>43.80500573863124</v>
+        <v>43.79899214254218</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92985853864528</v>
+        <v>99.932445698653</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.8109475107869</v>
+        <v>79.29290869968696</v>
       </c>
       <c r="C18" t="n">
-        <v>36.26099735518137</v>
+        <v>35.73944753465615</v>
       </c>
       <c r="D18" t="n">
-        <v>1.312691155921139</v>
+        <v>1.2840093428134</v>
       </c>
       <c r="E18" t="n">
-        <v>12.05313075263962</v>
+        <v>11.93676261558638</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581099862846524</v>
+        <v>0.7580940095695005</v>
       </c>
       <c r="G18" t="n">
-        <v>22.16366416147636</v>
+        <v>21.78599436689545</v>
       </c>
       <c r="H18" t="n">
-        <v>37.02884096960507</v>
+        <v>37.0985064157512</v>
       </c>
       <c r="I18" t="n">
-        <v>1.756323070580965</v>
+        <v>1.691454389261672</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738187414279079</v>
+        <v>4.738087559809377</v>
       </c>
       <c r="K18" t="n">
-        <v>20.18905248921311</v>
+        <v>20.70709130031302</v>
       </c>
       <c r="L18" t="n">
-        <v>43.4914489659076</v>
+        <v>43.49711941427672</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94149881030208</v>
+        <v>99.9436582492459</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.86379659563772</v>
+        <v>78.23519335808555</v>
       </c>
       <c r="C19" t="n">
-        <v>35.58437890097554</v>
+        <v>34.93774079744914</v>
       </c>
       <c r="D19" t="n">
-        <v>1.278488116814442</v>
+        <v>1.24577953695828</v>
       </c>
       <c r="E19" t="n">
-        <v>11.98316318860517</v>
+        <v>11.81712448940416</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585792588754072</v>
+        <v>0.7585509178841332</v>
       </c>
       <c r="G19" t="n">
-        <v>21.58617518499984</v>
+        <v>21.13734306255039</v>
       </c>
       <c r="H19" t="n">
-        <v>37.05176194472586</v>
+        <v>37.12086593294543</v>
       </c>
       <c r="I19" t="n">
-        <v>1.464508533645711</v>
+        <v>1.414586181567331</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741120367971296</v>
+        <v>4.740943236775832</v>
       </c>
       <c r="K19" t="n">
-        <v>21.13620340436226</v>
+        <v>21.76480664191445</v>
       </c>
       <c r="L19" t="n">
-        <v>43.23063094270162</v>
+        <v>43.25032809015008</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95121324803942</v>
+        <v>99.95287552951368</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.42622503824039</v>
+        <v>75.51382799182156</v>
       </c>
       <c r="C20" t="n">
-        <v>33.37223815490385</v>
+        <v>32.43390294352844</v>
       </c>
       <c r="D20" t="n">
-        <v>1.189692376408144</v>
+        <v>1.147247952939747</v>
       </c>
       <c r="E20" t="n">
-        <v>11.35440036126535</v>
+        <v>11.0790533811541</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589832568544319</v>
+        <v>0.758945839776092</v>
       </c>
       <c r="G20" t="n">
-        <v>20.08693527585775</v>
+        <v>19.46554172683299</v>
       </c>
       <c r="H20" t="n">
-        <v>37.07149467109537</v>
+        <v>37.14019204838443</v>
       </c>
       <c r="I20" t="n">
-        <v>1.221073741419127</v>
+        <v>1.179435544133618</v>
       </c>
       <c r="J20" t="n">
-        <v>4.7436453553402</v>
+        <v>4.743411498600574</v>
       </c>
       <c r="K20" t="n">
-        <v>23.57377496175963</v>
+        <v>24.48617200817844</v>
       </c>
       <c r="L20" t="n">
-        <v>43.01330609073525</v>
+        <v>43.04063098769404</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95931920739872</v>
+        <v>99.96070593940092</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.12839241909262</v>
+        <v>81.65854760279417</v>
       </c>
       <c r="C21" t="n">
-        <v>36.88044990375247</v>
+        <v>36.2781641207274</v>
       </c>
       <c r="D21" t="n">
-        <v>1.190550747169842</v>
+        <v>1.148028883731137</v>
       </c>
       <c r="E21" t="n">
-        <v>13.25721155727275</v>
+        <v>13.14054741485897</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595308681943228</v>
+        <v>0.7594624536203446</v>
       </c>
       <c r="G21" t="n">
-        <v>21.69976621479677</v>
+        <v>21.2548198866849</v>
       </c>
       <c r="H21" t="n">
-        <v>38.69658007973959</v>
+        <v>38.94150132899606</v>
       </c>
       <c r="I21" t="n">
-        <v>1.777685025704841</v>
+        <v>1.667547299775622</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747067926214518</v>
+        <v>4.746640335127153</v>
       </c>
       <c r="K21" t="n">
-        <v>17.87160758090738</v>
+        <v>18.34145239720582</v>
       </c>
       <c r="L21" t="n">
-        <v>45.18872907070079</v>
+        <v>45.32483638294151</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94078655536065</v>
+        <v>99.94445290087474</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_56_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.43877048612569</v>
+        <v>45.43258146356857</v>
       </c>
       <c r="M2" t="n">
-        <v>99.24720843859791</v>
+        <v>99.26179356969251</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99398307402248</v>
+        <v>87.96745625105372</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90449642333998</v>
+        <v>45.87166507568687</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228663447861512</v>
+        <v>2.228620254827494</v>
       </c>
       <c r="E3" t="n">
-        <v>5.690742453178022</v>
+        <v>5.670622298696281</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428878159538376</v>
+        <v>0.7428734182758315</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96507014600136</v>
+        <v>33.95393482417487</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17283953387653</v>
+        <v>34.17217724068824</v>
       </c>
       <c r="I3" t="n">
-        <v>6.550730827439739</v>
+        <v>6.556269350167057</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643048849711485</v>
+        <v>4.642958864223947</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00601692597751</v>
+        <v>12.03254374894626</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85434192001533</v>
+        <v>48.86044307293568</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648552693328</v>
+        <v>106.7646518975688</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05287406336087</v>
+        <v>87.06889561472921</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59607857836641</v>
+        <v>42.60808312495094</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183150644076909</v>
+        <v>2.185344218798523</v>
       </c>
       <c r="E4" t="n">
-        <v>6.486258059557808</v>
+        <v>6.473010013634762</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444439110057739</v>
+        <v>0.744430514377169</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27145013147268</v>
+        <v>33.29460683700728</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2444199062656</v>
+        <v>34.24380366134977</v>
       </c>
       <c r="I4" t="n">
-        <v>5.470376967196034</v>
+        <v>5.475009654704405</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652774443786086</v>
+        <v>4.652690714857306</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94712593663913</v>
+        <v>12.93110438527078</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2748307397878</v>
+        <v>44.27869389671807</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81803525479333</v>
+        <v>99.8178814069398</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.88954861076616</v>
+        <v>85.84661187755304</v>
       </c>
       <c r="C5" t="n">
-        <v>42.28175187229567</v>
+        <v>42.23552585423939</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126357908559771</v>
+        <v>2.12544041153172</v>
       </c>
       <c r="E5" t="n">
-        <v>7.078644932349406</v>
+        <v>7.057341911227398</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457633078643321</v>
+        <v>0.7457516684343204</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40592274667448</v>
+        <v>32.38194800100725</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30511216175928</v>
+        <v>34.30457674797873</v>
       </c>
       <c r="I5" t="n">
-        <v>4.566726879406819</v>
+        <v>4.570605209659136</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661020674152074</v>
+        <v>4.660947927714502</v>
       </c>
       <c r="K5" t="n">
-        <v>14.11045138923385</v>
+        <v>14.15338812244696</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45584182271504</v>
+        <v>43.45900242179408</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84804508424456</v>
+        <v>99.84791639848044</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.52616348409049</v>
+        <v>84.4778325456783</v>
       </c>
       <c r="C6" t="n">
-        <v>41.62757139091218</v>
+        <v>41.57650893944526</v>
       </c>
       <c r="D6" t="n">
-        <v>2.059778865416283</v>
+        <v>2.058540729941582</v>
       </c>
       <c r="E6" t="n">
-        <v>7.492224251405236</v>
+        <v>7.470969039646712</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468842021469612</v>
+        <v>0.7468741413490554</v>
       </c>
       <c r="G6" t="n">
-        <v>31.39125098329447</v>
+        <v>31.36270417804135</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35667329876021</v>
+        <v>34.35621050205654</v>
       </c>
       <c r="I6" t="n">
-        <v>3.811325619648808</v>
+        <v>3.814570571211461</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668026263418506</v>
+        <v>4.667963383431596</v>
       </c>
       <c r="K6" t="n">
-        <v>15.4738365159095</v>
+        <v>15.52216745432171</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77173856875037</v>
+        <v>42.77436235040918</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87314647557206</v>
+        <v>99.87303874417614</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.99393572618233</v>
+        <v>82.81215542928139</v>
       </c>
       <c r="C7" t="n">
-        <v>40.68726132486154</v>
+        <v>40.50321244080561</v>
       </c>
       <c r="D7" t="n">
-        <v>1.985227770872092</v>
+        <v>1.977219360428305</v>
       </c>
       <c r="E7" t="n">
-        <v>7.751079559832526</v>
+        <v>7.706313291917264</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478381723781051</v>
+        <v>0.7478310104590807</v>
       </c>
       <c r="G7" t="n">
-        <v>30.2550843009341</v>
+        <v>30.12374008162997</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40055592939284</v>
+        <v>34.40022648111771</v>
       </c>
       <c r="I7" t="n">
-        <v>3.180161415409504</v>
+        <v>3.182881388359802</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673988577363155</v>
+        <v>4.673943815369254</v>
       </c>
       <c r="K7" t="n">
-        <v>17.00606427381769</v>
+        <v>17.18784457071861</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20080424521939</v>
+        <v>42.20298269483102</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89412984389861</v>
+        <v>99.89403970635524</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.02653912251581</v>
+        <v>87.70396177952941</v>
       </c>
       <c r="C8" t="n">
-        <v>43.06110817642814</v>
+        <v>42.82092655074383</v>
       </c>
       <c r="D8" t="n">
-        <v>1.989522682423386</v>
+        <v>1.981452807221038</v>
       </c>
       <c r="E8" t="n">
-        <v>9.636515770584772</v>
+        <v>9.549569401932494</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494560717708959</v>
+        <v>0.7494321999153929</v>
       </c>
       <c r="G8" t="n">
-        <v>30.77877356691524</v>
+        <v>30.63215651306849</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47497930146122</v>
+        <v>34.47388119610807</v>
       </c>
       <c r="I8" t="n">
-        <v>5.713191280792201</v>
+        <v>5.63351841181271</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684100448568098</v>
+        <v>4.683951249471205</v>
       </c>
       <c r="K8" t="n">
-        <v>11.97346087748419</v>
+        <v>12.29603822047059</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77540235127054</v>
+        <v>44.695652489034</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80997140518286</v>
+        <v>99.81261726024843</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.152959601463</v>
+        <v>85.68161173209454</v>
       </c>
       <c r="C9" t="n">
-        <v>42.07418735964036</v>
+        <v>41.67269398745432</v>
       </c>
       <c r="D9" t="n">
-        <v>1.905128619673719</v>
+        <v>1.889864341922883</v>
       </c>
       <c r="E9" t="n">
-        <v>10.02270515246287</v>
+        <v>9.892025495914222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508391698670696</v>
+        <v>0.750803447413073</v>
       </c>
       <c r="G9" t="n">
-        <v>29.47316103446599</v>
+        <v>29.21624986438097</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53860181388521</v>
+        <v>34.53695858100136</v>
       </c>
       <c r="I9" t="n">
-        <v>4.76977899943895</v>
+        <v>4.703188455130332</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692744811669184</v>
+        <v>4.692521546331706</v>
       </c>
       <c r="K9" t="n">
-        <v>13.84704039853704</v>
+        <v>14.31838826790546</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92007248402282</v>
+        <v>43.85243112208987</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84130024220021</v>
+        <v>99.84351337744964</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.14603410711103</v>
+        <v>83.42229482161702</v>
       </c>
       <c r="C10" t="n">
-        <v>40.80737778759535</v>
+        <v>40.14284685792173</v>
       </c>
       <c r="D10" t="n">
-        <v>1.815635791677242</v>
+        <v>1.788519016821687</v>
       </c>
       <c r="E10" t="n">
-        <v>10.21540573126122</v>
+        <v>10.01580376816471</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520232835276309</v>
+        <v>0.7519810931635972</v>
       </c>
       <c r="G10" t="n">
-        <v>28.08866840560523</v>
+        <v>27.64950759877961</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59307104227103</v>
+        <v>34.59113028552547</v>
       </c>
       <c r="I10" t="n">
-        <v>3.981084330720992</v>
+        <v>3.925471226889458</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700145522047692</v>
+        <v>4.699881832272482</v>
       </c>
       <c r="K10" t="n">
-        <v>15.85396589288896</v>
+        <v>16.57770517838298</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20616245842019</v>
+        <v>43.14880383994167</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8675061389045</v>
+        <v>99.86935587624637</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.96444189033451</v>
+        <v>81.06866672653828</v>
       </c>
       <c r="C11" t="n">
-        <v>39.24306937456159</v>
+        <v>38.39738771891885</v>
       </c>
       <c r="D11" t="n">
-        <v>1.719226404332264</v>
+        <v>1.68408964214449</v>
       </c>
       <c r="E11" t="n">
-        <v>10.22664799286931</v>
+        <v>9.976932238459694</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530392772377923</v>
+        <v>0.7529939025708425</v>
       </c>
       <c r="G11" t="n">
-        <v>26.59717362194102</v>
+        <v>26.0350876448872</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63980675293846</v>
+        <v>34.63771951825876</v>
       </c>
       <c r="I11" t="n">
-        <v>3.322052358279461</v>
+        <v>3.275631889149533</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706495482736201</v>
+        <v>4.706211891067765</v>
       </c>
       <c r="K11" t="n">
-        <v>18.0355581096655</v>
+        <v>18.93133327346172</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61078683991956</v>
+        <v>42.56223814020583</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88941432414664</v>
+        <v>99.8909591325864</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.64080884106338</v>
+        <v>78.56690268435733</v>
       </c>
       <c r="C12" t="n">
-        <v>37.43385040798141</v>
+        <v>36.40228825937427</v>
       </c>
       <c r="D12" t="n">
-        <v>1.617454055758413</v>
+        <v>1.574145321715064</v>
       </c>
       <c r="E12" t="n">
-        <v>10.08319665443605</v>
+        <v>9.781073305946524</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539128306100839</v>
+        <v>0.7538669697707515</v>
       </c>
       <c r="G12" t="n">
-        <v>25.0227115161297</v>
+        <v>24.33540970209508</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67999020806388</v>
+        <v>34.67788060945457</v>
       </c>
       <c r="I12" t="n">
-        <v>2.771588384752227</v>
+        <v>2.732858214308136</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711955191313023</v>
+        <v>4.711668561067197</v>
       </c>
       <c r="K12" t="n">
-        <v>20.35919115893662</v>
+        <v>21.43309731564268</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11467920090755</v>
+        <v>42.07362465028447</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90772076782558</v>
+        <v>99.90901022530142</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.15164819400046</v>
+        <v>76.07293536755751</v>
       </c>
       <c r="C13" t="n">
-        <v>35.37305724108694</v>
+        <v>34.33009162360373</v>
       </c>
       <c r="D13" t="n">
-        <v>1.509326903269579</v>
+        <v>1.46561070748499</v>
       </c>
       <c r="E13" t="n">
-        <v>9.794460127348422</v>
+        <v>9.486627897102759</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546659013103798</v>
+        <v>0.7546200005654978</v>
       </c>
       <c r="G13" t="n">
-        <v>23.34993785424042</v>
+        <v>22.65752503178395</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71463146027749</v>
+        <v>34.7125200260129</v>
       </c>
       <c r="I13" t="n">
-        <v>2.311964064364299</v>
+        <v>2.279656701073047</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716661883189873</v>
+        <v>4.716375003534361</v>
       </c>
       <c r="K13" t="n">
-        <v>22.84835180599953</v>
+        <v>23.92706463244251</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70160238667042</v>
+        <v>41.66693101577854</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9230114337569</v>
+        <v>99.92408727182477</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.66664380949176</v>
+        <v>83.10601678298158</v>
       </c>
       <c r="C14" t="n">
-        <v>39.44064934358026</v>
+        <v>38.80597493536018</v>
       </c>
       <c r="D14" t="n">
-        <v>1.511087719767215</v>
+        <v>1.467252547992323</v>
       </c>
       <c r="E14" t="n">
-        <v>12.06838663780955</v>
+        <v>11.95328609512634</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555463124170473</v>
+        <v>0.7554653585300959</v>
       </c>
       <c r="G14" t="n">
-        <v>25.15164106884106</v>
+        <v>24.67344306532868</v>
       </c>
       <c r="H14" t="n">
-        <v>36.52959299549027</v>
+        <v>36.74194258637103</v>
       </c>
       <c r="I14" t="n">
-        <v>2.928224622560059</v>
+        <v>2.792968638820014</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722164452606544</v>
+        <v>4.721658490813099</v>
       </c>
       <c r="K14" t="n">
-        <v>16.33335619050827</v>
+        <v>16.89398321701841</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12850071700835</v>
+        <v>44.20704706976659</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90250625109688</v>
+        <v>99.90700522214519</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.76705857061333</v>
+        <v>82.24421901323966</v>
       </c>
       <c r="C15" t="n">
-        <v>38.97638106737402</v>
+        <v>38.36853883960502</v>
       </c>
       <c r="D15" t="n">
-        <v>1.47540472746471</v>
+        <v>1.43460078957992</v>
       </c>
       <c r="E15" t="n">
-        <v>12.20791077079678</v>
+        <v>12.08258955578883</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562895582285908</v>
+        <v>0.7561786755779123</v>
       </c>
       <c r="G15" t="n">
-        <v>24.57511784579381</v>
+        <v>24.13139773109017</v>
       </c>
       <c r="H15" t="n">
-        <v>36.58293828366421</v>
+        <v>36.78366405182653</v>
       </c>
       <c r="I15" t="n">
-        <v>2.442587645736555</v>
+        <v>2.329671487014347</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726809738928692</v>
+        <v>4.726116722361952</v>
       </c>
       <c r="K15" t="n">
-        <v>17.23294142938666</v>
+        <v>17.75578098676035</v>
       </c>
       <c r="L15" t="n">
-        <v>43.70933793039043</v>
+        <v>43.79809771144519</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91866042715111</v>
+        <v>99.92241753781055</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.17523481392472</v>
+        <v>79.62625131518693</v>
       </c>
       <c r="C16" t="n">
-        <v>36.76214742972534</v>
+        <v>36.11036453829166</v>
       </c>
       <c r="D16" t="n">
-        <v>1.376618182061155</v>
+        <v>1.335928760639122</v>
       </c>
       <c r="E16" t="n">
-        <v>11.73005892663335</v>
+        <v>11.57537613755295</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569301232262658</v>
+        <v>0.756793729848771</v>
       </c>
       <c r="G16" t="n">
-        <v>22.92967714082678</v>
+        <v>22.47163705578673</v>
       </c>
       <c r="H16" t="n">
-        <v>36.61392343944437</v>
+        <v>36.81358284007538</v>
       </c>
       <c r="I16" t="n">
-        <v>2.037213731568646</v>
+        <v>1.942971979729173</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730813270164161</v>
+        <v>4.729960811554819</v>
       </c>
       <c r="K16" t="n">
-        <v>19.82476518607529</v>
+        <v>20.37374868481306</v>
       </c>
       <c r="L16" t="n">
-        <v>43.34523772737336</v>
+        <v>43.45117368003377</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93215034317397</v>
+        <v>99.9352869031385</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.85285510841871</v>
+        <v>81.34541917252467</v>
       </c>
       <c r="C17" t="n">
-        <v>37.98630866452952</v>
+        <v>37.37722471174031</v>
       </c>
       <c r="D17" t="n">
-        <v>1.377755262668465</v>
+        <v>1.33697021197567</v>
       </c>
       <c r="E17" t="n">
-        <v>12.505778018668</v>
+        <v>12.36216316145669</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575553442028772</v>
+        <v>0.7573837043029964</v>
       </c>
       <c r="G17" t="n">
-        <v>23.37659656407796</v>
+        <v>22.94984583491761</v>
       </c>
       <c r="H17" t="n">
-        <v>37.07214599038526</v>
+        <v>37.30297218440241</v>
       </c>
       <c r="I17" t="n">
-        <v>2.028303027148171</v>
+        <v>1.902435923575563</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734720901267981</v>
+        <v>4.733648151893727</v>
       </c>
       <c r="K17" t="n">
-        <v>18.14714489158129</v>
+        <v>18.65458082747534</v>
       </c>
       <c r="L17" t="n">
-        <v>43.79899214254218</v>
+        <v>43.9048293276195</v>
       </c>
       <c r="M17" t="n">
-        <v>99.932445698653</v>
+        <v>99.93663486683516</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.29290869968696</v>
+        <v>78.8015537911885</v>
       </c>
       <c r="C18" t="n">
-        <v>35.73944753465615</v>
+        <v>35.12672474292452</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2840093428134</v>
+        <v>1.245003847704182</v>
       </c>
       <c r="E18" t="n">
-        <v>11.93676261558638</v>
+        <v>11.77620977253219</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580940095695005</v>
+        <v>0.7578919574248597</v>
       </c>
       <c r="G18" t="n">
-        <v>21.78599436689545</v>
+        <v>21.37119145419687</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0985064157512</v>
+        <v>37.32800487517696</v>
       </c>
       <c r="I18" t="n">
-        <v>1.691454389261672</v>
+        <v>1.586427150248047</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738087559809377</v>
+        <v>4.736824733905373</v>
       </c>
       <c r="K18" t="n">
-        <v>20.70709130031302</v>
+        <v>21.19844620881151</v>
       </c>
       <c r="L18" t="n">
-        <v>43.49711941427672</v>
+        <v>43.62198360594243</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9436582492459</v>
+        <v>99.94715455767846</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.23519335808555</v>
+        <v>77.74637135866401</v>
       </c>
       <c r="C19" t="n">
-        <v>34.93774079744914</v>
+        <v>34.31545170353476</v>
       </c>
       <c r="D19" t="n">
-        <v>1.24577953695828</v>
+        <v>1.207490698758575</v>
       </c>
       <c r="E19" t="n">
-        <v>11.81712448940416</v>
+        <v>11.64184344652537</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585509178841332</v>
+        <v>0.7583217817948809</v>
       </c>
       <c r="G19" t="n">
-        <v>21.13734306255039</v>
+        <v>20.72725714857627</v>
       </c>
       <c r="H19" t="n">
-        <v>37.12086593294543</v>
+        <v>37.34917476096666</v>
       </c>
       <c r="I19" t="n">
-        <v>1.414586181567331</v>
+        <v>1.322772385824253</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740943236775832</v>
+        <v>4.739511136218005</v>
       </c>
       <c r="K19" t="n">
-        <v>21.76480664191445</v>
+        <v>22.25362864133598</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25032809015008</v>
+        <v>43.38685223428904</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95287552951368</v>
+        <v>99.95593257915976</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.51382799182156</v>
+        <v>75.01819266333254</v>
       </c>
       <c r="C20" t="n">
-        <v>32.43390294352844</v>
+        <v>31.79045276724367</v>
       </c>
       <c r="D20" t="n">
-        <v>1.147247952939747</v>
+        <v>1.10992281577164</v>
       </c>
       <c r="E20" t="n">
-        <v>11.0790533811541</v>
+        <v>10.88496551135058</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758945839776092</v>
+        <v>0.7586933874557523</v>
       </c>
       <c r="G20" t="n">
-        <v>19.46554172683299</v>
+        <v>19.05244954782908</v>
       </c>
       <c r="H20" t="n">
-        <v>37.14019204838443</v>
+        <v>37.36747723506572</v>
       </c>
       <c r="I20" t="n">
-        <v>1.179435544133618</v>
+        <v>1.102850494261319</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743411498600574</v>
+        <v>4.741833671598452</v>
       </c>
       <c r="K20" t="n">
-        <v>24.48617200817844</v>
+        <v>24.98180733666744</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04063098769404</v>
+        <v>43.19099621870488</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96070593940092</v>
+        <v>99.963256322616</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.65854760279417</v>
+        <v>81.20764069971065</v>
       </c>
       <c r="C21" t="n">
-        <v>36.2781641207274</v>
+        <v>35.71347061326767</v>
       </c>
       <c r="D21" t="n">
-        <v>1.148028883731137</v>
+        <v>1.110609570452533</v>
       </c>
       <c r="E21" t="n">
-        <v>13.14054741485897</v>
+        <v>12.97224523571321</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594624536203446</v>
+        <v>0.759162822111743</v>
       </c>
       <c r="G21" t="n">
-        <v>21.2548198866849</v>
+        <v>20.89355037119226</v>
       </c>
       <c r="H21" t="n">
-        <v>38.94150132899606</v>
+        <v>39.21991031578605</v>
       </c>
       <c r="I21" t="n">
-        <v>1.667547299775622</v>
+        <v>1.507394746256462</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746640335127153</v>
+        <v>4.744767638198394</v>
       </c>
       <c r="K21" t="n">
-        <v>18.34145239720582</v>
+        <v>18.79235930028934</v>
       </c>
       <c r="L21" t="n">
-        <v>45.32483638294151</v>
+        <v>45.44395466523776</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94445290087474</v>
+        <v>99.94978457879478</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_56_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.43258146356857</v>
+        <v>43.14052443947639</v>
       </c>
       <c r="M2" t="n">
-        <v>99.26179356969251</v>
+        <v>96.11831433591109</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96745625105372</v>
+        <v>81.50045245620481</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87166507568687</v>
+        <v>43.25600801176036</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228620254827494</v>
+        <v>2.180741416500793</v>
       </c>
       <c r="E3" t="n">
-        <v>5.670622298696281</v>
+        <v>4.164344576001953</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428734182758315</v>
+        <v>0.7376495963512798</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95393482417487</v>
+        <v>32.80198547319942</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17217724068824</v>
+        <v>33.93188143215887</v>
       </c>
       <c r="I3" t="n">
-        <v>6.556269350167057</v>
+        <v>3.073539984796999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642958864223947</v>
+        <v>4.610309977195499</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03254374894626</v>
+        <v>18.49954754379518</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86044307293568</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646518975688</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.06889561472921</v>
+        <v>88.56091164907822</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60808312495094</v>
+        <v>42.74647238450798</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185344218798523</v>
+        <v>2.18653331575272</v>
       </c>
       <c r="E4" t="n">
-        <v>6.473010013634762</v>
+        <v>6.480325566626087</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744430514377169</v>
+        <v>0.7396087429575505</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29460683700728</v>
+        <v>33.45353645052806</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24380366134977</v>
+        <v>34.02200217604732</v>
       </c>
       <c r="I4" t="n">
-        <v>5.475009654704405</v>
+        <v>7.056350753681805</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652690714857306</v>
+        <v>4.622554643484691</v>
       </c>
       <c r="K4" t="n">
-        <v>12.93110438527078</v>
+        <v>11.43908835092175</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27869389671807</v>
+        <v>45.57985062407944</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8178814069398</v>
+        <v>99.76541135950917</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.84661187755304</v>
+        <v>87.50347891649844</v>
       </c>
       <c r="C5" t="n">
-        <v>42.23552585423939</v>
+        <v>42.78262005907373</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12544041153172</v>
+        <v>2.136426027998278</v>
       </c>
       <c r="E5" t="n">
-        <v>7.057341911227398</v>
+        <v>7.314069355483899</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457516684343204</v>
+        <v>0.7412692024934532</v>
       </c>
       <c r="G5" t="n">
-        <v>32.38194800100725</v>
+        <v>32.6869046479144</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30457674797873</v>
+        <v>34.09838331469885</v>
       </c>
       <c r="I5" t="n">
-        <v>4.570605209659136</v>
+        <v>5.893493852325467</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660947927714502</v>
+        <v>4.632932515584083</v>
       </c>
       <c r="K5" t="n">
-        <v>14.15338812244696</v>
+        <v>12.49652108350158</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45900242179408</v>
+        <v>44.52484911426685</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84791639848044</v>
+        <v>99.80399025684216</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.4778325456783</v>
+        <v>86.17168788575975</v>
       </c>
       <c r="C6" t="n">
-        <v>41.57650893944526</v>
+        <v>42.36541901597433</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058540729941582</v>
+        <v>2.072840293743211</v>
       </c>
       <c r="E6" t="n">
-        <v>7.470969039646712</v>
+        <v>7.916481981195311</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468741413490554</v>
+        <v>0.7426801392402118</v>
       </c>
       <c r="G6" t="n">
-        <v>31.36270417804135</v>
+        <v>31.71405522306894</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35621050205654</v>
+        <v>34.16328640504975</v>
       </c>
       <c r="I6" t="n">
-        <v>3.814570571211461</v>
+        <v>4.920592973211002</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667963383431596</v>
+        <v>4.641750870251324</v>
       </c>
       <c r="K6" t="n">
-        <v>15.52216745432171</v>
+        <v>13.82831211424026</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77436235040918</v>
+        <v>43.64256070722082</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87303874417614</v>
+        <v>99.83629183743541</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.81215542928139</v>
+        <v>84.7211396235753</v>
       </c>
       <c r="C7" t="n">
-        <v>40.50321244080561</v>
+        <v>41.67892506578699</v>
       </c>
       <c r="D7" t="n">
-        <v>1.977219360428305</v>
+        <v>2.003974771857928</v>
       </c>
       <c r="E7" t="n">
-        <v>7.706313291917264</v>
+        <v>8.337994470815225</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478310104590807</v>
+        <v>0.7438802634271728</v>
       </c>
       <c r="G7" t="n">
-        <v>30.12374008162997</v>
+        <v>30.66042606956991</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40022648111771</v>
+        <v>34.21849211764995</v>
       </c>
       <c r="I7" t="n">
-        <v>3.182881388359802</v>
+        <v>4.107120283835274</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673943815369254</v>
+        <v>4.649251646419831</v>
       </c>
       <c r="K7" t="n">
-        <v>17.18784457071861</v>
+        <v>15.2788603764247</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20298269483102</v>
+        <v>42.90553141964357</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89403970635524</v>
+        <v>99.86331686185527</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.70396177952941</v>
+        <v>83.19306433789232</v>
       </c>
       <c r="C8" t="n">
-        <v>42.82092655074383</v>
+        <v>40.78863366274216</v>
       </c>
       <c r="D8" t="n">
-        <v>1.981452807221038</v>
+        <v>1.931940099908409</v>
       </c>
       <c r="E8" t="n">
-        <v>9.549569401932494</v>
+        <v>8.609494485215775</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494321999153929</v>
+        <v>0.7449017832858118</v>
       </c>
       <c r="G8" t="n">
-        <v>30.63215651306849</v>
+        <v>29.55830953358863</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47388119610807</v>
+        <v>34.26548203114734</v>
       </c>
       <c r="I8" t="n">
-        <v>5.63351841181271</v>
+        <v>3.427300259210047</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683951249471205</v>
+        <v>4.655636145536325</v>
       </c>
       <c r="K8" t="n">
-        <v>12.29603822047059</v>
+        <v>16.80693566210767</v>
       </c>
       <c r="L8" t="n">
-        <v>44.695652489034</v>
+        <v>42.29034400059918</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81261726024843</v>
+        <v>99.88591332544901</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.68161173209454</v>
+        <v>81.41403508547234</v>
       </c>
       <c r="C9" t="n">
-        <v>41.67269398745432</v>
+        <v>39.5416305744689</v>
       </c>
       <c r="D9" t="n">
-        <v>1.889864341922883</v>
+        <v>1.848390824563942</v>
       </c>
       <c r="E9" t="n">
-        <v>9.892025495914222</v>
+        <v>8.713736851517288</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750803447413073</v>
+        <v>0.7457738657087598</v>
       </c>
       <c r="G9" t="n">
-        <v>29.21624986438097</v>
+        <v>28.28002179472143</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53695858100136</v>
+        <v>34.30559782260296</v>
       </c>
       <c r="I9" t="n">
-        <v>4.703188455130332</v>
+        <v>2.859427265678194</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692521546331706</v>
+        <v>4.66108666067975</v>
       </c>
       <c r="K9" t="n">
-        <v>14.31838826790546</v>
+        <v>18.58596491452768</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85243112208987</v>
+        <v>41.77720172602537</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84351337744964</v>
+        <v>99.90479721502196</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.42229482161702</v>
+        <v>85.87849193472866</v>
       </c>
       <c r="C10" t="n">
-        <v>40.14284685792173</v>
+        <v>42.65805745417315</v>
       </c>
       <c r="D10" t="n">
-        <v>1.788519016821687</v>
+        <v>1.850446269143136</v>
       </c>
       <c r="E10" t="n">
-        <v>10.01580376816471</v>
+        <v>10.49894692344243</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519810931635972</v>
+        <v>0.7466031799583246</v>
       </c>
       <c r="G10" t="n">
-        <v>27.64950759877961</v>
+        <v>29.60949762577778</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59113028552547</v>
+        <v>35.64177420498125</v>
       </c>
       <c r="I10" t="n">
-        <v>3.925471226889458</v>
+        <v>2.864953856686216</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699881832272482</v>
+        <v>4.66626987473953</v>
       </c>
       <c r="K10" t="n">
-        <v>16.57770517838298</v>
+        <v>14.12150806527133</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14880383994167</v>
+        <v>43.12504209675053</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86935587624637</v>
+        <v>99.90460761619501</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.06866672653828</v>
+        <v>85.66875135519336</v>
       </c>
       <c r="C11" t="n">
-        <v>38.39738771891885</v>
+        <v>42.8324064378222</v>
       </c>
       <c r="D11" t="n">
-        <v>1.68408964214449</v>
+        <v>1.839810683056606</v>
       </c>
       <c r="E11" t="n">
-        <v>9.976932238459694</v>
+        <v>10.84678244776124</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529939025708425</v>
+        <v>0.7473146360555629</v>
       </c>
       <c r="G11" t="n">
-        <v>26.0350876448872</v>
+        <v>29.43931469951337</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63771951825876</v>
+        <v>35.67573810743334</v>
       </c>
       <c r="I11" t="n">
-        <v>3.275631889149533</v>
+        <v>2.449074306025998</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706211891067765</v>
+        <v>4.67071647534727</v>
       </c>
       <c r="K11" t="n">
-        <v>18.93133327346172</v>
+        <v>14.33124864480662</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56223814020583</v>
+        <v>42.75478682583406</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8909591325864</v>
+        <v>99.91844190846288</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.56690268435733</v>
+        <v>83.87913328259893</v>
       </c>
       <c r="C12" t="n">
-        <v>36.40228825937427</v>
+        <v>41.42375360296258</v>
       </c>
       <c r="D12" t="n">
-        <v>1.574145321715064</v>
+        <v>1.763080682247264</v>
       </c>
       <c r="E12" t="n">
-        <v>9.781073305946524</v>
+        <v>10.7348385906171</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538669697707515</v>
+        <v>0.7479212346374212</v>
       </c>
       <c r="G12" t="n">
-        <v>24.33540970209508</v>
+        <v>28.2115369387237</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67788060945457</v>
+        <v>35.70469626119966</v>
       </c>
       <c r="I12" t="n">
-        <v>2.732858214308136</v>
+        <v>2.042551858689903</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711668561067197</v>
+        <v>4.674507716483884</v>
       </c>
       <c r="K12" t="n">
-        <v>21.43309731564268</v>
+        <v>16.12086671740109</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07362465028447</v>
+        <v>42.38734983780228</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90901022530142</v>
+        <v>99.93197015816594</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.07293536755751</v>
+        <v>84.90127008739843</v>
       </c>
       <c r="C13" t="n">
-        <v>34.33009162360373</v>
+        <v>42.31280888739141</v>
       </c>
       <c r="D13" t="n">
-        <v>1.46561070748499</v>
+        <v>1.764379741496171</v>
       </c>
       <c r="E13" t="n">
-        <v>9.486627897102759</v>
+        <v>11.3271697327854</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546200005654978</v>
+        <v>0.7484723120821992</v>
       </c>
       <c r="G13" t="n">
-        <v>22.65752503178395</v>
+        <v>28.50396369225567</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7125200260129</v>
+        <v>36.00264406548069</v>
       </c>
       <c r="I13" t="n">
-        <v>2.279656701073047</v>
+        <v>1.876688592784556</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716375003534361</v>
+        <v>4.677951950513747</v>
       </c>
       <c r="K13" t="n">
-        <v>23.92706463244251</v>
+        <v>15.09872991260157</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66693101577854</v>
+        <v>42.52595097187577</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92408727182477</v>
+        <v>99.93748977186875</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.10601678298158</v>
+        <v>83.01215188497856</v>
       </c>
       <c r="C14" t="n">
-        <v>38.80597493536018</v>
+        <v>40.71551846964185</v>
       </c>
       <c r="D14" t="n">
-        <v>1.467252547992323</v>
+        <v>1.685306320602514</v>
       </c>
       <c r="E14" t="n">
-        <v>11.95328609512634</v>
+        <v>11.0803399936776</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554653585300959</v>
+        <v>0.7489426354922739</v>
       </c>
       <c r="G14" t="n">
-        <v>24.67344306532868</v>
+        <v>27.2265142491647</v>
       </c>
       <c r="H14" t="n">
-        <v>36.74194258637103</v>
+        <v>36.02526732896719</v>
       </c>
       <c r="I14" t="n">
-        <v>2.792968638820014</v>
+        <v>1.564889885247567</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721658490813099</v>
+        <v>4.680891471826714</v>
       </c>
       <c r="K14" t="n">
-        <v>16.89398321701841</v>
+        <v>16.98784811502145</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20704706976659</v>
+        <v>42.24450317664824</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90700522214519</v>
+        <v>99.94786976131154</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.24421901323966</v>
+        <v>82.11541371444248</v>
       </c>
       <c r="C15" t="n">
-        <v>38.36853883960502</v>
+        <v>40.03434544666371</v>
       </c>
       <c r="D15" t="n">
-        <v>1.43460078957992</v>
+        <v>1.647067357075969</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08258955578883</v>
+        <v>11.05081069882006</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561786755779123</v>
+        <v>0.7493473706308984</v>
       </c>
       <c r="G15" t="n">
-        <v>24.13139773109017</v>
+        <v>26.60875492992323</v>
       </c>
       <c r="H15" t="n">
-        <v>36.78366405182653</v>
+        <v>36.04473569793885</v>
       </c>
       <c r="I15" t="n">
-        <v>2.329671487014347</v>
+        <v>1.331276593610353</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726116722361952</v>
+        <v>4.683421066443117</v>
       </c>
       <c r="K15" t="n">
-        <v>17.75578098676035</v>
+        <v>17.88458628555753</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79809771144519</v>
+        <v>42.03671634948893</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92241753781055</v>
+        <v>99.95564808171017</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.62625131518693</v>
+        <v>79.79575987380218</v>
       </c>
       <c r="C16" t="n">
-        <v>36.11036453829166</v>
+        <v>37.9212260427002</v>
       </c>
       <c r="D16" t="n">
-        <v>1.335928760639122</v>
+        <v>1.550585403613094</v>
       </c>
       <c r="E16" t="n">
-        <v>11.57537613755295</v>
+        <v>10.58846128408709</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756793729848771</v>
+        <v>0.7496948031627425</v>
       </c>
       <c r="G16" t="n">
-        <v>22.47163705578673</v>
+        <v>25.05006660802512</v>
       </c>
       <c r="H16" t="n">
-        <v>36.81358284007538</v>
+        <v>36.06144772532963</v>
       </c>
       <c r="I16" t="n">
-        <v>1.942971979729173</v>
+        <v>1.109911529817373</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729960811554819</v>
+        <v>4.685592519767143</v>
       </c>
       <c r="K16" t="n">
-        <v>20.37374868481306</v>
+        <v>20.20424012619781</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45117368003377</v>
+        <v>41.83755392572393</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9352869031385</v>
+        <v>99.96302009462194</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.34541917252467</v>
+        <v>84.07411819413939</v>
       </c>
       <c r="C17" t="n">
-        <v>37.37722471174031</v>
+        <v>40.76298025769967</v>
       </c>
       <c r="D17" t="n">
-        <v>1.33697021197567</v>
+        <v>1.551331258292944</v>
       </c>
       <c r="E17" t="n">
-        <v>12.36216316145669</v>
+        <v>12.10742206404075</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573837043029964</v>
+        <v>0.7500554175320605</v>
       </c>
       <c r="G17" t="n">
-        <v>22.94984583491761</v>
+        <v>26.37377911862712</v>
       </c>
       <c r="H17" t="n">
-        <v>37.30297218440241</v>
+        <v>37.39045687429724</v>
       </c>
       <c r="I17" t="n">
-        <v>1.902435923575563</v>
+        <v>1.213227101773894</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733648151893727</v>
+        <v>4.687846359575381</v>
       </c>
       <c r="K17" t="n">
-        <v>18.65458082747534</v>
+        <v>15.92588180586063</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9048293276195</v>
+        <v>43.27071647637173</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93663486683516</v>
+        <v>99.95957853993202</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.8015537911885</v>
+        <v>85.49611102140159</v>
       </c>
       <c r="C18" t="n">
-        <v>35.12672474292452</v>
+        <v>41.46896742270299</v>
       </c>
       <c r="D18" t="n">
-        <v>1.245003847704182</v>
+        <v>1.552472801127366</v>
       </c>
       <c r="E18" t="n">
-        <v>11.77620977253219</v>
+        <v>12.67910783013955</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578919574248597</v>
+        <v>0.7506073437455795</v>
       </c>
       <c r="G18" t="n">
-        <v>21.37119145419687</v>
+        <v>26.51729427317294</v>
       </c>
       <c r="H18" t="n">
-        <v>37.32800487517696</v>
+        <v>37.41797053902388</v>
       </c>
       <c r="I18" t="n">
-        <v>1.586427150248047</v>
+        <v>1.887362335782391</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736824733905373</v>
+        <v>4.691295898409875</v>
       </c>
       <c r="K18" t="n">
-        <v>21.19844620881151</v>
+        <v>14.50388897859842</v>
       </c>
       <c r="L18" t="n">
-        <v>43.62198360594243</v>
+        <v>43.96427778047842</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94715455767846</v>
+        <v>99.93713418177983</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.74637135866401</v>
+        <v>82.94418549141355</v>
       </c>
       <c r="C19" t="n">
-        <v>34.31545170353476</v>
+        <v>39.20969037594496</v>
       </c>
       <c r="D19" t="n">
-        <v>1.207490698758575</v>
+        <v>1.456168558162538</v>
       </c>
       <c r="E19" t="n">
-        <v>11.64184344652537</v>
+        <v>12.15488665306416</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583217817948809</v>
+        <v>0.7510820820102559</v>
       </c>
       <c r="G19" t="n">
-        <v>20.72725714857627</v>
+        <v>24.87235212114358</v>
       </c>
       <c r="H19" t="n">
-        <v>37.34917476096666</v>
+        <v>37.44163636450431</v>
       </c>
       <c r="I19" t="n">
-        <v>1.322772385824253</v>
+        <v>1.573796699964593</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739511136218005</v>
+        <v>4.694263012564102</v>
       </c>
       <c r="K19" t="n">
-        <v>22.25362864133598</v>
+        <v>17.05581450858645</v>
       </c>
       <c r="L19" t="n">
-        <v>43.38685223428904</v>
+        <v>43.68206838391909</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95593257915976</v>
+        <v>99.9475732684505</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.01819266333254</v>
+        <v>80.26385717918707</v>
       </c>
       <c r="C20" t="n">
-        <v>31.79045276724367</v>
+        <v>36.77274397714915</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10992281577164</v>
+        <v>1.355486249997929</v>
       </c>
       <c r="E20" t="n">
-        <v>10.88496551135058</v>
+        <v>11.53317629388338</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586933874557523</v>
+        <v>0.751491389896297</v>
       </c>
       <c r="G20" t="n">
-        <v>19.05244954782908</v>
+        <v>23.15262962953892</v>
       </c>
       <c r="H20" t="n">
-        <v>37.36747723506572</v>
+        <v>37.46204046865929</v>
       </c>
       <c r="I20" t="n">
-        <v>1.102850494261319</v>
+        <v>1.3122119603594</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741833671598452</v>
+        <v>4.696821186851859</v>
       </c>
       <c r="K20" t="n">
-        <v>24.98180733666744</v>
+        <v>19.73614282081293</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19099621870488</v>
+        <v>43.44739662703891</v>
       </c>
       <c r="M20" t="n">
-        <v>99.963256322616</v>
+        <v>99.95628342500099</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.20764069971065</v>
+        <v>77.54289432948181</v>
       </c>
       <c r="C21" t="n">
-        <v>35.71347061326767</v>
+        <v>34.2540723747723</v>
       </c>
       <c r="D21" t="n">
-        <v>1.110609570452533</v>
+        <v>1.253742199083066</v>
       </c>
       <c r="E21" t="n">
-        <v>12.97224523571321</v>
+        <v>10.84982279206622</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759162822111743</v>
+        <v>0.7518448071016115</v>
       </c>
       <c r="G21" t="n">
-        <v>20.89355037119226</v>
+        <v>21.41477184762163</v>
       </c>
       <c r="H21" t="n">
-        <v>39.21991031578605</v>
+        <v>37.47965840790093</v>
       </c>
       <c r="I21" t="n">
-        <v>1.507394746256462</v>
+        <v>1.09402423132329</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744767638198394</v>
+        <v>4.699030044385074</v>
       </c>
       <c r="K21" t="n">
-        <v>18.79235930028934</v>
+        <v>22.45710567051817</v>
       </c>
       <c r="L21" t="n">
-        <v>45.44395466523776</v>
+        <v>43.25237162247731</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94978457879478</v>
+        <v>99.96354966776779</v>
       </c>
     </row>
   </sheetData>
